--- a/Configs/GameConfig/Datas/实体组.xlsx
+++ b/Configs/GameConfig/Datas/实体组.xlsx
@@ -136,7 +136,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -154,13 +154,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -664,52 +657,52 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -718,79 +711,79 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -799,7 +792,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="23" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="22" applyBorder="1" applyAlignment="1">

--- a/Configs/GameConfig/Datas/实体组.xlsx
+++ b/Configs/GameConfig/Datas/实体组.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
   <si>
     <t>##var</t>
   </si>
@@ -114,16 +114,7 @@
     <t>Effect</t>
   </si>
   <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
     <t>Bullet</t>
-  </si>
-  <si>
-    <t>Unrecycle</t>
   </si>
 </sst>
 </file>
@@ -1139,7 +1130,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AJ15"/>
+  <dimension ref="A1:AJ13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9.225" customWidth="1"/>
@@ -1495,24 +1486,12 @@
       <c r="N9" s="14"/>
     </row>
     <row r="10" spans="1:36">
-      <c r="B10" s="4">
-        <v>5</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="4">
-        <v>60</v>
-      </c>
-      <c r="E10" s="4">
-        <v>1</v>
-      </c>
-      <c r="F10" s="4">
-        <v>60</v>
-      </c>
-      <c r="G10" s="4">
-        <v>0</v>
-      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
       <c r="H10" s="13"/>
       <c r="J10" s="13"/>
       <c r="L10" s="13"/>
@@ -1520,50 +1499,20 @@
       <c r="N10" s="14"/>
     </row>
     <row r="11" spans="1:36">
-      <c r="B11" s="4">
-        <v>6</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="4">
-        <v>60</v>
-      </c>
-      <c r="E11" s="4">
-        <v>60</v>
-      </c>
-      <c r="F11" s="4">
-        <v>60</v>
-      </c>
-      <c r="G11" s="4">
-        <v>0</v>
-      </c>
-      <c r="H11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="H11" s="15"/>
       <c r="J11" s="13"/>
       <c r="L11" s="13"/>
       <c r="M11" s="14"/>
       <c r="N11" s="14"/>
     </row>
     <row r="12" spans="1:36">
-      <c r="B12" s="4">
-        <v>7</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="4">
-        <v>60</v>
-      </c>
-      <c r="E12" s="4">
-        <v>0</v>
-      </c>
-      <c r="F12" s="4">
-        <v>60</v>
-      </c>
-      <c r="G12" s="4">
-        <v>0</v>
-      </c>
-      <c r="H12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="H12" s="15"/>
       <c r="J12" s="13"/>
       <c r="L12" s="13"/>
       <c r="M12" s="14"/>
@@ -1573,31 +1522,11 @@
       <c r="C13" s="13"/>
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
-      <c r="H13" s="15"/>
+      <c r="H13" s="13"/>
       <c r="J13" s="13"/>
       <c r="L13" s="13"/>
       <c r="M13" s="14"/>
       <c r="N13" s="14"/>
-    </row>
-    <row r="14" spans="1:36">
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="H14" s="15"/>
-      <c r="J14" s="13"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="14"/>
-    </row>
-    <row r="15" spans="1:36">
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="2">
